--- a/src/fixtures/sample/gstr2b-2026-02.xlsx
+++ b/src/fixtures/sample/gstr2b-2026-02.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O44"/>
+  <dimension ref="A1:O45"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -470,10 +470,10 @@
         <v>Mahesh Steel Traders</v>
       </c>
       <c r="C6" t="str">
-        <v>S01/2025/032</v>
+        <v>S01/2026/051</v>
       </c>
       <c r="D6" t="str">
-        <v>03/12/2025</v>
+        <v>10/02/2026</v>
       </c>
       <c r="E6">
         <v>566400</v>
@@ -497,7 +497,7 @@
         <v>2026-03</v>
       </c>
       <c r="L6" t="str">
-        <v>19/03/2026</v>
+        <v>16/03/2026</v>
       </c>
       <c r="M6" t="str">
         <v>Yes</v>
@@ -511,31 +511,31 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>24AAGCA1188M1ZI</v>
+        <v>27AAPFM4821K1ZV</v>
       </c>
       <c r="B7" t="str">
-        <v>Anand Polymers</v>
+        <v>Mahesh Steel Traders</v>
       </c>
       <c r="C7" t="str">
-        <v>S05/2026/051</v>
+        <v>S01/2026/053</v>
       </c>
       <c r="D7" t="str">
-        <v>24/02/2026</v>
+        <v>18/02/2026</v>
       </c>
       <c r="E7">
-        <v>359900</v>
+        <v>560500</v>
       </c>
       <c r="F7">
-        <v>305000</v>
+        <v>475000</v>
       </c>
       <c r="G7">
-        <v>54900</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>42750</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>42750</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -544,7 +544,7 @@
         <v>2026-03</v>
       </c>
       <c r="L7" t="str">
-        <v>10/03/2026</v>
+        <v>12/03/2026</v>
       </c>
       <c r="M7" t="str">
         <v>Yes</v>
@@ -564,19 +564,19 @@
         <v>Anand Polymers</v>
       </c>
       <c r="C8" t="str">
-        <v>S05/2026/052</v>
+        <v>S05/2026/051</v>
       </c>
       <c r="D8" t="str">
-        <v>24/02/2026</v>
+        <v>04/02/2026</v>
       </c>
       <c r="E8">
-        <v>375240</v>
+        <v>359900</v>
       </c>
       <c r="F8">
-        <v>318000</v>
+        <v>305000</v>
       </c>
       <c r="G8">
-        <v>57240</v>
+        <v>54900</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -591,7 +591,7 @@
         <v>2026-03</v>
       </c>
       <c r="L8" t="str">
-        <v>12/03/2026</v>
+        <v>08/03/2026</v>
       </c>
       <c r="M8" t="str">
         <v>Yes</v>
@@ -611,19 +611,19 @@
         <v>Anand Polymers</v>
       </c>
       <c r="C9" t="str">
-        <v>S05/2026/053</v>
+        <v>S05/2026/052</v>
       </c>
       <c r="D9" t="str">
-        <v>19/02/2026</v>
+        <v>14/02/2026</v>
       </c>
       <c r="E9">
-        <v>359900</v>
+        <v>376420</v>
       </c>
       <c r="F9">
-        <v>305000</v>
+        <v>319000</v>
       </c>
       <c r="G9">
-        <v>54900</v>
+        <v>57420</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -638,7 +638,7 @@
         <v>2026-03</v>
       </c>
       <c r="L9" t="str">
-        <v>16/03/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="M9" t="str">
         <v>Yes</v>
@@ -652,31 +652,31 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>27AABFS9034J1ZY</v>
+        <v>24AAGCA1188M1ZI</v>
       </c>
       <c r="B10" t="str">
-        <v>Surya Electricals</v>
+        <v>Anand Polymers</v>
       </c>
       <c r="C10" t="str">
-        <v>SE 51</v>
+        <v>S05/2026/053</v>
       </c>
       <c r="D10" t="str">
-        <v>22/02/2026</v>
+        <v>10/02/2026</v>
       </c>
       <c r="E10">
-        <v>161660</v>
+        <v>375240</v>
       </c>
       <c r="F10">
-        <v>137000</v>
+        <v>318000</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>57240</v>
       </c>
       <c r="H10">
-        <v>12330</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>12330</v>
+        <v>0</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -685,7 +685,7 @@
         <v>2026-03</v>
       </c>
       <c r="L10" t="str">
-        <v>11/03/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="M10" t="str">
         <v>Yes</v>
@@ -708,22 +708,22 @@
         <v>SE 51</v>
       </c>
       <c r="D11" t="str">
-        <v>08/02/2026</v>
+        <v>10/02/2026</v>
       </c>
       <c r="E11">
-        <v>160480</v>
+        <v>167560</v>
       </c>
       <c r="F11">
-        <v>136000</v>
+        <v>142000</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>12240</v>
+        <v>12780</v>
       </c>
       <c r="I11">
-        <v>12240</v>
+        <v>12780</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -732,7 +732,7 @@
         <v>2026-03</v>
       </c>
       <c r="L11" t="str">
-        <v>15/03/2026</v>
+        <v>12/03/2026</v>
       </c>
       <c r="M11" t="str">
         <v>Yes</v>
@@ -746,31 +746,31 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>27AAJFN2276C1ZC</v>
+        <v>27AABFS9034J1ZY</v>
       </c>
       <c r="B12" t="str">
-        <v>Nilkanth Traders</v>
+        <v>Surya Electricals</v>
       </c>
       <c r="C12" t="str">
-        <v>S07/2026/051</v>
+        <v>SE 51</v>
       </c>
       <c r="D12" t="str">
-        <v>03/02/2026</v>
+        <v>23/02/2026</v>
       </c>
       <c r="E12">
-        <v>237180</v>
+        <v>166380</v>
       </c>
       <c r="F12">
-        <v>201000</v>
+        <v>141000</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12">
-        <v>18090</v>
+        <v>12690</v>
       </c>
       <c r="I12">
-        <v>18090</v>
+        <v>12690</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -779,7 +779,7 @@
         <v>2026-03</v>
       </c>
       <c r="L12" t="str">
-        <v>12/03/2026</v>
+        <v>09/03/2026</v>
       </c>
       <c r="M12" t="str">
         <v>Yes</v>
@@ -799,25 +799,25 @@
         <v>Nilkanth Traders</v>
       </c>
       <c r="C13" t="str">
-        <v>S07/2026/052</v>
+        <v>S07/2026/051</v>
       </c>
       <c r="D13" t="str">
-        <v>13/02/2026</v>
+        <v>14/02/2026</v>
       </c>
       <c r="E13">
-        <v>252520</v>
+        <v>227740</v>
       </c>
       <c r="F13">
-        <v>214000</v>
+        <v>193000</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>19260</v>
+        <v>17370</v>
       </c>
       <c r="I13">
-        <v>19260</v>
+        <v>17370</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -826,7 +826,7 @@
         <v>2026-03</v>
       </c>
       <c r="L13" t="str">
-        <v>11/03/2026</v>
+        <v>15/03/2026</v>
       </c>
       <c r="M13" t="str">
         <v>Yes</v>
@@ -840,31 +840,31 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>24AAECR8890P1ZI</v>
+        <v>27AAJFN2276C1ZC</v>
       </c>
       <c r="B14" t="str">
-        <v>Ratna Chemicals</v>
+        <v>Nilkanth Traders</v>
       </c>
       <c r="C14" t="str">
-        <v>S08/2026/051</v>
+        <v>S07/2026/052</v>
       </c>
       <c r="D14" t="str">
         <v>21/02/2026</v>
       </c>
       <c r="E14">
-        <v>223020</v>
+        <v>253700</v>
       </c>
       <c r="F14">
-        <v>189000</v>
+        <v>215000</v>
       </c>
       <c r="G14">
-        <v>34020</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>19350</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>19350</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -873,7 +873,7 @@
         <v>2026-03</v>
       </c>
       <c r="L14" t="str">
-        <v>12/03/2026</v>
+        <v>15/03/2026</v>
       </c>
       <c r="M14" t="str">
         <v>Yes</v>
@@ -893,19 +893,19 @@
         <v>Ratna Chemicals</v>
       </c>
       <c r="C15" t="str">
-        <v>S08/2026/052</v>
+        <v>S08/2026/051</v>
       </c>
       <c r="D15" t="str">
-        <v>23/02/2026</v>
+        <v>25/02/2026</v>
       </c>
       <c r="E15">
-        <v>217120</v>
+        <v>214760</v>
       </c>
       <c r="F15">
-        <v>184000</v>
+        <v>182000</v>
       </c>
       <c r="G15">
-        <v>33120</v>
+        <v>32760</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>2026-03</v>
       </c>
       <c r="L15" t="str">
-        <v>13/03/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="M15" t="str">
         <v>Yes</v>
@@ -934,31 +934,31 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>27AAACM6543N1Z3</v>
+        <v>24AAECR8890P1ZI</v>
       </c>
       <c r="B16" t="str">
-        <v>Metro Motors</v>
+        <v>Ratna Chemicals</v>
       </c>
       <c r="C16" t="str">
-        <v>S09/2026/051</v>
+        <v>S08/2026/052</v>
       </c>
       <c r="D16" t="str">
-        <v>17/02/2026</v>
+        <v>10/02/2026</v>
       </c>
       <c r="E16">
-        <v>1047840</v>
+        <v>210040</v>
       </c>
       <c r="F16">
-        <v>888000</v>
+        <v>178000</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>32040</v>
       </c>
       <c r="H16">
-        <v>79920</v>
+        <v>0</v>
       </c>
       <c r="I16">
-        <v>79920</v>
+        <v>0</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -967,13 +967,13 @@
         <v>2026-03</v>
       </c>
       <c r="L16" t="str">
-        <v>10/03/2026</v>
+        <v>14/03/2026</v>
       </c>
       <c r="M16" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="N16" t="str">
-        <v>ITC unavailable - blocked credit</v>
+        <v/>
       </c>
       <c r="O16" t="str">
         <v>N</v>
@@ -981,31 +981,31 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>27AAFCV4412Q2ZU</v>
+        <v>27AAACM6543N1Z3</v>
       </c>
       <c r="B17" t="str">
-        <v>Vindhya Alloys</v>
+        <v>Metro Motors</v>
       </c>
       <c r="C17" t="str">
-        <v>S10/2026/051</v>
+        <v>S09/2026/051</v>
       </c>
       <c r="D17" t="str">
-        <v>14/02/2026</v>
+        <v>06/02/2026</v>
       </c>
       <c r="E17">
-        <v>323320</v>
+        <v>1064360</v>
       </c>
       <c r="F17">
-        <v>274000</v>
+        <v>902000</v>
       </c>
       <c r="G17">
-        <v>49320</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>81180</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>81180</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -1017,10 +1017,10 @@
         <v>14/03/2026</v>
       </c>
       <c r="M17" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="N17" t="str">
-        <v/>
+        <v>ITC unavailable - blocked credit</v>
       </c>
       <c r="O17" t="str">
         <v>N</v>
@@ -1034,19 +1034,19 @@
         <v>Vindhya Alloys</v>
       </c>
       <c r="C18" t="str">
-        <v>S10/2026/052</v>
+        <v>S10/2026/051</v>
       </c>
       <c r="D18" t="str">
-        <v>10/02/2026</v>
+        <v>07/02/2026</v>
       </c>
       <c r="E18">
-        <v>297360</v>
+        <v>323320</v>
       </c>
       <c r="F18">
-        <v>252000</v>
+        <v>274000</v>
       </c>
       <c r="G18">
-        <v>45360</v>
+        <v>49320</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -1061,7 +1061,7 @@
         <v>2026-03</v>
       </c>
       <c r="L18" t="str">
-        <v>15/03/2026</v>
+        <v>12/03/2026</v>
       </c>
       <c r="M18" t="str">
         <v>Yes</v>
@@ -1075,31 +1075,31 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>27AAFCB2210G1Z8</v>
+        <v>27AAFCV4412Q2ZU</v>
       </c>
       <c r="B19" t="str">
-        <v>Bharat Office Supplies</v>
+        <v>Vindhya Alloys</v>
       </c>
       <c r="C19" t="str">
-        <v>S12/2026/051</v>
+        <v>S10/2026/052</v>
       </c>
       <c r="D19" t="str">
-        <v>03/02/2026</v>
+        <v>19/02/2026</v>
       </c>
       <c r="E19">
-        <v>199420</v>
+        <v>312700</v>
       </c>
       <c r="F19">
-        <v>169000</v>
+        <v>265000</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>47700</v>
       </c>
       <c r="H19">
-        <v>15210</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>15210</v>
+        <v>0</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -1128,25 +1128,25 @@
         <v>Bharat Office Supplies</v>
       </c>
       <c r="C20" t="str">
-        <v>S12/2026/052</v>
+        <v>S12/2026/051</v>
       </c>
       <c r="D20" t="str">
-        <v>26/02/2026</v>
+        <v>12/02/2026</v>
       </c>
       <c r="E20">
-        <v>184080</v>
+        <v>189980</v>
       </c>
       <c r="F20">
-        <v>156000</v>
+        <v>161000</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20">
-        <v>14040</v>
+        <v>14490</v>
       </c>
       <c r="I20">
-        <v>14040</v>
+        <v>14490</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -1169,31 +1169,31 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>27AAGFK5561R1ZL</v>
+        <v>27AAFCB2210G1Z8</v>
       </c>
       <c r="B21" t="str">
-        <v>Konkan Hardware</v>
+        <v>Bharat Office Supplies</v>
       </c>
       <c r="C21" t="str">
-        <v>S13/2026/051</v>
+        <v>S12/2026/052</v>
       </c>
       <c r="D21" t="str">
-        <v>07/02/2026</v>
+        <v>08/02/2026</v>
       </c>
       <c r="E21">
-        <v>86140</v>
+        <v>195880</v>
       </c>
       <c r="F21">
-        <v>73000</v>
+        <v>166000</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21">
-        <v>6570</v>
+        <v>14940</v>
       </c>
       <c r="I21">
-        <v>6570</v>
+        <v>14940</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -1202,7 +1202,7 @@
         <v>2026-03</v>
       </c>
       <c r="L21" t="str">
-        <v>09/03/2026</v>
+        <v>16/03/2026</v>
       </c>
       <c r="M21" t="str">
         <v>Yes</v>
@@ -1216,31 +1216,31 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>24AAACT3398E1ZE</v>
+        <v>27AAGFK5561R1ZL</v>
       </c>
       <c r="B22" t="str">
-        <v>Trident Paper Mills</v>
+        <v>Konkan Hardware</v>
       </c>
       <c r="C22" t="str">
-        <v>S14/2026/051</v>
+        <v>S13/2026/051</v>
       </c>
       <c r="D22" t="str">
-        <v>04/02/2026</v>
+        <v>07/02/2026</v>
       </c>
       <c r="E22">
-        <v>142780</v>
+        <v>75520</v>
       </c>
       <c r="F22">
-        <v>121000</v>
+        <v>64000</v>
       </c>
       <c r="G22">
-        <v>21780</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>5760</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>5760</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -1249,7 +1249,7 @@
         <v>2026-03</v>
       </c>
       <c r="L22" t="str">
-        <v>13/03/2026</v>
+        <v>16/03/2026</v>
       </c>
       <c r="M22" t="str">
         <v>Yes</v>
@@ -1263,25 +1263,25 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>33AAJFL7745T1ZE</v>
+        <v>24AAACT3398E1ZE</v>
       </c>
       <c r="B23" t="str">
-        <v>Lakshmi Fasteners</v>
+        <v>Trident Paper Mills</v>
       </c>
       <c r="C23" t="str">
-        <v>S15/2026/051</v>
+        <v>S14/2026/051</v>
       </c>
       <c r="D23" t="str">
-        <v>25/02/2026</v>
+        <v>09/02/2026</v>
       </c>
       <c r="E23">
-        <v>56640</v>
+        <v>143960</v>
       </c>
       <c r="F23">
-        <v>48000</v>
+        <v>122000</v>
       </c>
       <c r="G23">
-        <v>8640</v>
+        <v>21960</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -1296,7 +1296,7 @@
         <v>2026-03</v>
       </c>
       <c r="L23" t="str">
-        <v>12/03/2026</v>
+        <v>13/03/2026</v>
       </c>
       <c r="M23" t="str">
         <v>Yes</v>
@@ -1316,19 +1316,19 @@
         <v>Lakshmi Fasteners</v>
       </c>
       <c r="C24" t="str">
-        <v>S15/2026/052</v>
+        <v>S15/2026/051</v>
       </c>
       <c r="D24" t="str">
-        <v>19/02/2026</v>
+        <v>13/02/2026</v>
       </c>
       <c r="E24">
-        <v>30680</v>
+        <v>54280</v>
       </c>
       <c r="F24">
-        <v>26000</v>
+        <v>46000</v>
       </c>
       <c r="G24">
-        <v>4680</v>
+        <v>8280</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -1343,7 +1343,7 @@
         <v>2026-03</v>
       </c>
       <c r="L24" t="str">
-        <v>16/03/2026</v>
+        <v>13/03/2026</v>
       </c>
       <c r="M24" t="str">
         <v>Yes</v>
@@ -1363,19 +1363,19 @@
         <v>Lakshmi Fasteners</v>
       </c>
       <c r="C25" t="str">
-        <v>S15/2026/053</v>
+        <v>S15/2026/052</v>
       </c>
       <c r="D25" t="str">
-        <v>18/02/2026</v>
+        <v>09/02/2026</v>
       </c>
       <c r="E25">
-        <v>48380</v>
+        <v>57820</v>
       </c>
       <c r="F25">
-        <v>41000</v>
+        <v>49000</v>
       </c>
       <c r="G25">
-        <v>7380</v>
+        <v>8820</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -1404,25 +1404,25 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>29AAECO9912W1Z8</v>
+        <v>33AAJFL7745T1ZE</v>
       </c>
       <c r="B26" t="str">
-        <v>Orion Software Services</v>
+        <v>Lakshmi Fasteners</v>
       </c>
       <c r="C26" t="str">
-        <v>S16/2026/051</v>
+        <v>S15/2026/053</v>
       </c>
       <c r="D26" t="str">
-        <v>22/02/2026</v>
+        <v>19/02/2026</v>
       </c>
       <c r="E26">
-        <v>60180</v>
+        <v>46020</v>
       </c>
       <c r="F26">
-        <v>51000</v>
+        <v>39000</v>
       </c>
       <c r="G26">
-        <v>9180</v>
+        <v>7020</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -1457,10 +1457,10 @@
         <v>Orion Software Services</v>
       </c>
       <c r="C27" t="str">
-        <v>S16/2026/052</v>
+        <v>S16/2026/051</v>
       </c>
       <c r="D27" t="str">
-        <v>19/02/2026</v>
+        <v>02/02/2026</v>
       </c>
       <c r="E27">
         <v>61360</v>
@@ -1484,7 +1484,7 @@
         <v>2026-03</v>
       </c>
       <c r="L27" t="str">
-        <v>09/03/2026</v>
+        <v>14/03/2026</v>
       </c>
       <c r="M27" t="str">
         <v>Yes</v>
@@ -1498,25 +1498,25 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>09AAHFG4423Y1ZH</v>
+        <v>29AAECO9912W1Z8</v>
       </c>
       <c r="B28" t="str">
-        <v>Ganga Textiles</v>
+        <v>Orion Software Services</v>
       </c>
       <c r="C28" t="str">
-        <v>S17/2026/051</v>
+        <v>S16/2026/052</v>
       </c>
       <c r="D28" t="str">
-        <v>08/02/2026</v>
+        <v>04/02/2026</v>
       </c>
       <c r="E28">
-        <v>48380</v>
+        <v>68440</v>
       </c>
       <c r="F28">
-        <v>41000</v>
+        <v>58000</v>
       </c>
       <c r="G28">
-        <v>7380</v>
+        <v>10440</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -1531,7 +1531,7 @@
         <v>2026-03</v>
       </c>
       <c r="L28" t="str">
-        <v>08/03/2026</v>
+        <v>14/03/2026</v>
       </c>
       <c r="M28" t="str">
         <v>Yes</v>
@@ -1545,31 +1545,31 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>27AAKFP6678U1ZU</v>
+        <v>09AAHFG4423Y1ZH</v>
       </c>
       <c r="B29" t="str">
-        <v>Pinnacle Safety Gear</v>
+        <v>Ganga Textiles</v>
       </c>
       <c r="C29" t="str">
-        <v>S18/2026/051</v>
+        <v>S17/2026/051</v>
       </c>
       <c r="D29" t="str">
-        <v>18/02/2026</v>
+        <v>08/02/2026</v>
       </c>
       <c r="E29">
-        <v>164020</v>
+        <v>42480</v>
       </c>
       <c r="F29">
-        <v>139000</v>
+        <v>36000</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>6480</v>
       </c>
       <c r="H29">
-        <v>12510</v>
+        <v>0</v>
       </c>
       <c r="I29">
-        <v>12510</v>
+        <v>0</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -1578,7 +1578,7 @@
         <v>2026-03</v>
       </c>
       <c r="L29" t="str">
-        <v>15/03/2026</v>
+        <v>08/03/2026</v>
       </c>
       <c r="M29" t="str">
         <v>Yes</v>
@@ -1598,25 +1598,25 @@
         <v>Pinnacle Safety Gear</v>
       </c>
       <c r="C30" t="str">
-        <v>S18/2026/052</v>
+        <v>S18/2026/051</v>
       </c>
       <c r="D30" t="str">
-        <v>14/02/2026</v>
+        <v>09/02/2026</v>
       </c>
       <c r="E30">
-        <v>161660</v>
+        <v>171100</v>
       </c>
       <c r="F30">
-        <v>137000</v>
+        <v>145000</v>
       </c>
       <c r="G30">
         <v>0</v>
       </c>
       <c r="H30">
-        <v>12330</v>
+        <v>13050</v>
       </c>
       <c r="I30">
-        <v>12330</v>
+        <v>13050</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -1625,7 +1625,7 @@
         <v>2026-03</v>
       </c>
       <c r="L30" t="str">
-        <v>16/03/2026</v>
+        <v>13/03/2026</v>
       </c>
       <c r="M30" t="str">
         <v>Yes</v>
@@ -1645,25 +1645,25 @@
         <v>Pinnacle Safety Gear</v>
       </c>
       <c r="C31" t="str">
-        <v>S18/2026/053</v>
+        <v>S18/2026/052</v>
       </c>
       <c r="D31" t="str">
-        <v>06/02/2026</v>
+        <v>14/02/2026</v>
       </c>
       <c r="E31">
-        <v>155760</v>
+        <v>162840</v>
       </c>
       <c r="F31">
-        <v>132000</v>
+        <v>138000</v>
       </c>
       <c r="G31">
         <v>0</v>
       </c>
       <c r="H31">
-        <v>11880</v>
+        <v>12420</v>
       </c>
       <c r="I31">
-        <v>11880</v>
+        <v>12420</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -1672,7 +1672,7 @@
         <v>2026-03</v>
       </c>
       <c r="L31" t="str">
-        <v>08/03/2026</v>
+        <v>15/03/2026</v>
       </c>
       <c r="M31" t="str">
         <v>Yes</v>
@@ -1686,31 +1686,31 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>33AABFS2234V1ZT</v>
+        <v>27AAKFP6678U1ZU</v>
       </c>
       <c r="B32" t="str">
-        <v>Sundar Printing Works</v>
+        <v>Pinnacle Safety Gear</v>
       </c>
       <c r="C32" t="str">
-        <v>S19/2026/051</v>
+        <v>S18/2026/053</v>
       </c>
       <c r="D32" t="str">
-        <v>04/02/2026</v>
+        <v>13/02/2026</v>
       </c>
       <c r="E32">
-        <v>116820</v>
+        <v>168740</v>
       </c>
       <c r="F32">
-        <v>99000</v>
+        <v>143000</v>
       </c>
       <c r="G32">
-        <v>17820</v>
+        <v>0</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>12870</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>12870</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -1719,7 +1719,7 @@
         <v>2026-03</v>
       </c>
       <c r="L32" t="str">
-        <v>16/03/2026</v>
+        <v>13/03/2026</v>
       </c>
       <c r="M32" t="str">
         <v>Yes</v>
@@ -1739,19 +1739,19 @@
         <v>Sundar Printing Works</v>
       </c>
       <c r="C33" t="str">
-        <v>S19/2026/052</v>
+        <v>S19/2026/042</v>
       </c>
       <c r="D33" t="str">
-        <v>18/02/2026</v>
+        <v>04/01/2026</v>
       </c>
       <c r="E33">
-        <v>113280</v>
+        <v>101480</v>
       </c>
       <c r="F33">
-        <v>96000</v>
+        <v>86000</v>
       </c>
       <c r="G33">
-        <v>17280</v>
+        <v>15480</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -1766,7 +1766,7 @@
         <v>2026-03</v>
       </c>
       <c r="L33" t="str">
-        <v>16/03/2026</v>
+        <v>12/03/2026</v>
       </c>
       <c r="M33" t="str">
         <v>Yes</v>
@@ -1780,31 +1780,31 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>27AAFCA8801X1ZT</v>
+        <v>33AABFS2234V1ZT</v>
       </c>
       <c r="B34" t="str">
-        <v>Ashoka Civil Works</v>
+        <v>Sundar Printing Works</v>
       </c>
       <c r="C34" t="str">
-        <v>S20/2026/051</v>
+        <v>S19/2026/051</v>
       </c>
       <c r="D34" t="str">
-        <v>24/02/2026</v>
+        <v>25/02/2026</v>
       </c>
       <c r="E34">
-        <v>145140</v>
+        <v>107380</v>
       </c>
       <c r="F34">
-        <v>123000</v>
+        <v>91000</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>16380</v>
       </c>
       <c r="H34">
-        <v>11070</v>
+        <v>0</v>
       </c>
       <c r="I34">
-        <v>11070</v>
+        <v>0</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -1813,7 +1813,7 @@
         <v>2026-03</v>
       </c>
       <c r="L34" t="str">
-        <v>10/03/2026</v>
+        <v>14/03/2026</v>
       </c>
       <c r="M34" t="str">
         <v>Yes</v>
@@ -1827,31 +1827,31 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>27AAFCA8801X1ZT</v>
+        <v>33AABFS2234V1ZT</v>
       </c>
       <c r="B35" t="str">
-        <v>Ashoka Civil Works</v>
+        <v>Sundar Printing Works</v>
       </c>
       <c r="C35" t="str">
-        <v>S20/2026/052</v>
+        <v>S19/2026/052</v>
       </c>
       <c r="D35" t="str">
-        <v>18/02/2026</v>
+        <v>15/02/2026</v>
       </c>
       <c r="E35">
-        <v>154580</v>
+        <v>96760</v>
       </c>
       <c r="F35">
-        <v>131000</v>
+        <v>82000</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>14760</v>
       </c>
       <c r="H35">
-        <v>11790</v>
+        <v>0</v>
       </c>
       <c r="I35">
-        <v>11790</v>
+        <v>0</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>2026-03</v>
       </c>
       <c r="L35" t="str">
-        <v>10/03/2026</v>
+        <v>11/03/2026</v>
       </c>
       <c r="M35" t="str">
         <v>Yes</v>
@@ -1874,31 +1874,31 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>29AADCN3345Z1ZD</v>
+        <v>27AAFCA8801X1ZT</v>
       </c>
       <c r="B36" t="str">
-        <v>Nova Instruments</v>
+        <v>Ashoka Civil Works</v>
       </c>
       <c r="C36" t="str">
-        <v>S21/2026/051</v>
+        <v>S20/2026/051</v>
       </c>
       <c r="D36" t="str">
-        <v>03/02/2026</v>
+        <v>24/02/2026</v>
       </c>
       <c r="E36">
-        <v>187620</v>
+        <v>149860</v>
       </c>
       <c r="F36">
-        <v>159000</v>
+        <v>127000</v>
       </c>
       <c r="G36">
-        <v>28620</v>
+        <v>0</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>11430</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>11430</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -1907,7 +1907,7 @@
         <v>2026-03</v>
       </c>
       <c r="L36" t="str">
-        <v>12/03/2026</v>
+        <v>14/03/2026</v>
       </c>
       <c r="M36" t="str">
         <v>Yes</v>
@@ -1921,31 +1921,31 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>29AADCN3345Z1ZD</v>
+        <v>27AAFCA8801X1ZT</v>
       </c>
       <c r="B37" t="str">
-        <v>Nova Instruments</v>
+        <v>Ashoka Civil Works</v>
       </c>
       <c r="C37" t="str">
-        <v>S21/2026/052</v>
+        <v>S20/2026/052</v>
       </c>
       <c r="D37" t="str">
-        <v>08/02/2026</v>
+        <v>12/02/2026</v>
       </c>
       <c r="E37">
-        <v>187620</v>
+        <v>142780</v>
       </c>
       <c r="F37">
-        <v>159000</v>
+        <v>121000</v>
       </c>
       <c r="G37">
-        <v>28620</v>
+        <v>0</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>10890</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>10890</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -1974,19 +1974,19 @@
         <v>Nova Instruments</v>
       </c>
       <c r="C38" t="str">
-        <v>S21/2026/053</v>
+        <v>S21/2026/051</v>
       </c>
       <c r="D38" t="str">
         <v>10/02/2026</v>
       </c>
       <c r="E38">
-        <v>200600</v>
+        <v>184080</v>
       </c>
       <c r="F38">
-        <v>170000</v>
+        <v>156000</v>
       </c>
       <c r="G38">
-        <v>30600</v>
+        <v>28080</v>
       </c>
       <c r="H38">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>2026-03</v>
       </c>
       <c r="L38" t="str">
-        <v>12/03/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="M38" t="str">
         <v>Yes</v>
@@ -2015,31 +2015,31 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>27AAGFM1167A1ZO</v>
+        <v>29AADCN3345Z1ZD</v>
       </c>
       <c r="B39" t="str">
-        <v>Meridian Housekeeping</v>
+        <v>Nova Instruments</v>
       </c>
       <c r="C39" t="str">
-        <v>S22/2026/051</v>
+        <v>S21/2026/052</v>
       </c>
       <c r="D39" t="str">
-        <v>14/02/2026</v>
+        <v>24/02/2026</v>
       </c>
       <c r="E39">
-        <v>193520</v>
+        <v>210040</v>
       </c>
       <c r="F39">
-        <v>164000</v>
+        <v>178000</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>32040</v>
       </c>
       <c r="H39">
-        <v>14760</v>
+        <v>0</v>
       </c>
       <c r="I39">
-        <v>14760</v>
+        <v>0</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -2048,7 +2048,7 @@
         <v>2026-03</v>
       </c>
       <c r="L39" t="str">
-        <v>16/03/2026</v>
+        <v>12/03/2026</v>
       </c>
       <c r="M39" t="str">
         <v>Yes</v>
@@ -2062,25 +2062,25 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>24AAECC7789B1ZM</v>
+        <v>29AADCN3345Z1ZD</v>
       </c>
       <c r="B40" t="str">
-        <v>Coral Adhesives</v>
+        <v>Nova Instruments</v>
       </c>
       <c r="C40" t="str">
-        <v>S23/2026/051</v>
+        <v>S21/2026/053</v>
       </c>
       <c r="D40" t="str">
-        <v>20/02/2026</v>
+        <v>14/02/2026</v>
       </c>
       <c r="E40">
-        <v>192340</v>
+        <v>182900</v>
       </c>
       <c r="F40">
-        <v>163000</v>
+        <v>155000</v>
       </c>
       <c r="G40">
-        <v>29340</v>
+        <v>27900</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -2095,7 +2095,7 @@
         <v>2026-03</v>
       </c>
       <c r="L40" t="str">
-        <v>15/03/2026</v>
+        <v>09/03/2026</v>
       </c>
       <c r="M40" t="str">
         <v>Yes</v>
@@ -2109,25 +2109,25 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>09AAJFY5523C1Z3</v>
+        <v>24AAECC7789B1ZM</v>
       </c>
       <c r="B41" t="str">
-        <v>Yamuna Agro Products</v>
+        <v>Coral Adhesives</v>
       </c>
       <c r="C41" t="str">
-        <v>S24/2026/051</v>
+        <v>S23/2026/051</v>
       </c>
       <c r="D41" t="str">
-        <v>12/02/2026</v>
+        <v>26/02/2026</v>
       </c>
       <c r="E41">
-        <v>158120</v>
+        <v>197060</v>
       </c>
       <c r="F41">
-        <v>134000</v>
+        <v>167000</v>
       </c>
       <c r="G41">
-        <v>24120</v>
+        <v>30060</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -2142,7 +2142,7 @@
         <v>2026-03</v>
       </c>
       <c r="L41" t="str">
-        <v>11/03/2026</v>
+        <v>13/03/2026</v>
       </c>
       <c r="M41" t="str">
         <v>Yes</v>
@@ -2162,19 +2162,19 @@
         <v>Yamuna Agro Products</v>
       </c>
       <c r="C42" t="str">
-        <v>S24/2026/052</v>
+        <v>S24/2026/051</v>
       </c>
       <c r="D42" t="str">
-        <v>09/02/2026</v>
+        <v>04/02/2026</v>
       </c>
       <c r="E42">
-        <v>167560</v>
+        <v>145140</v>
       </c>
       <c r="F42">
-        <v>142000</v>
+        <v>123000</v>
       </c>
       <c r="G42">
-        <v>25560</v>
+        <v>22140</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -2189,7 +2189,7 @@
         <v>2026-03</v>
       </c>
       <c r="L42" t="str">
-        <v>13/03/2026</v>
+        <v>09/03/2026</v>
       </c>
       <c r="M42" t="str">
         <v>Yes</v>
@@ -2209,19 +2209,19 @@
         <v>Yamuna Agro Products</v>
       </c>
       <c r="C43" t="str">
-        <v>S24/2026/053</v>
+        <v>S24/2026/052</v>
       </c>
       <c r="D43" t="str">
-        <v>03/02/2026</v>
+        <v>18/02/2026</v>
       </c>
       <c r="E43">
-        <v>145140</v>
+        <v>156940</v>
       </c>
       <c r="F43">
-        <v>123000</v>
+        <v>133000</v>
       </c>
       <c r="G43">
-        <v>22140</v>
+        <v>23940</v>
       </c>
       <c r="H43">
         <v>0</v>
@@ -2236,7 +2236,7 @@
         <v>2026-03</v>
       </c>
       <c r="L43" t="str">
-        <v>09/03/2026</v>
+        <v>11/03/2026</v>
       </c>
       <c r="M43" t="str">
         <v>Yes</v>
@@ -2250,61 +2250,108 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
+        <v>09AAJFY5523C1Z3</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Yamuna Agro Products</v>
+      </c>
+      <c r="C44" t="str">
+        <v>S24/2026/053</v>
+      </c>
+      <c r="D44" t="str">
+        <v>05/02/2026</v>
+      </c>
+      <c r="E44">
+        <v>167560</v>
+      </c>
+      <c r="F44">
+        <v>142000</v>
+      </c>
+      <c r="G44">
+        <v>25560</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44" t="str">
+        <v>2026-03</v>
+      </c>
+      <c r="L44" t="str">
+        <v>12/03/2026</v>
+      </c>
+      <c r="M44" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
+        <v>N</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
         <v>27AABCZ9934D1Z1</v>
       </c>
-      <c r="B44" t="str">
+      <c r="B45" t="str">
         <v>Zenith Tooling</v>
       </c>
-      <c r="C44" t="str">
+      <c r="C45" t="str">
         <v>S25/2026/051</v>
       </c>
-      <c r="D44" t="str">
-        <v>20/02/2026</v>
-      </c>
-      <c r="E44">
-        <v>54280</v>
-      </c>
-      <c r="F44">
-        <v>46000</v>
-      </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
-      <c r="H44">
-        <v>4140</v>
-      </c>
-      <c r="I44">
-        <v>4140</v>
-      </c>
-      <c r="J44">
-        <v>0</v>
-      </c>
-      <c r="K44" t="str">
-        <v>2026-03</v>
-      </c>
-      <c r="L44" t="str">
-        <v>09/03/2026</v>
-      </c>
-      <c r="M44" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="N44" t="str">
-        <v/>
-      </c>
-      <c r="O44" t="str">
+      <c r="D45" t="str">
+        <v>18/02/2026</v>
+      </c>
+      <c r="E45">
+        <v>51920</v>
+      </c>
+      <c r="F45">
+        <v>44000</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>3960</v>
+      </c>
+      <c r="I45">
+        <v>3960</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45" t="str">
+        <v>2026-03</v>
+      </c>
+      <c r="L45" t="str">
+        <v>14/03/2026</v>
+      </c>
+      <c r="M45" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
         <v>N</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O44"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O45"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2363,9 +2410,103 @@
         <v>Supply Attract Reverse Charge</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>24AAECR8890P1ZI</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Ratna Chemicals</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Debit note</v>
+      </c>
+      <c r="D5" t="str">
+        <v>S08/2026/051/DN</v>
+      </c>
+      <c r="E5" t="str">
+        <v>26/02/2026</v>
+      </c>
+      <c r="F5">
+        <v>21476</v>
+      </c>
+      <c r="G5">
+        <v>18200</v>
+      </c>
+      <c r="H5">
+        <v>3276</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5" t="str">
+        <v>2026-03</v>
+      </c>
+      <c r="M5" t="str">
+        <v>14/03/2026</v>
+      </c>
+      <c r="N5" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="O5" t="str">
+        <v>N</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>24AAECR8890P1ZI</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Ratna Chemicals</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Debit note</v>
+      </c>
+      <c r="D6" t="str">
+        <v>S08/2026/052/DN</v>
+      </c>
+      <c r="E6" t="str">
+        <v>26/02/2026</v>
+      </c>
+      <c r="F6">
+        <v>21004</v>
+      </c>
+      <c r="G6">
+        <v>17800</v>
+      </c>
+      <c r="H6">
+        <v>3204</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6" t="str">
+        <v>2026-03</v>
+      </c>
+      <c r="M6" t="str">
+        <v>22/03/2026</v>
+      </c>
+      <c r="N6" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="O6" t="str">
+        <v>N</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O6"/>
   </ignoredErrors>
 </worksheet>
 </file>